--- a/data/trans_dic/P3A$otraNOcobra-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 13,5</t>
+          <t>9,04; 13,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 17,26</t>
+          <t>13,45; 17,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 15,45</t>
+          <t>12,31; 15,21</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,87</t>
+          <t>1,24; 2,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,69</t>
+          <t>0,88; 1,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,09</t>
+          <t>1,19; 2,11</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,27</t>
+          <t>0,19; 1,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,98</t>
+          <t>0,1; 0,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,85</t>
+          <t>0,19; 0,83</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,69</t>
+          <t>2,31; 3,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 4,59</t>
+          <t>3,3; 4,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,99</t>
+          <t>3,09; 4,07</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47714; 69533</t>
+          <t>46574; 70118</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>102484; 130389</t>
+          <t>101652; 130175</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>156352; 196323</t>
+          <t>156426; 193177</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29283; 65780</t>
+          <t>28289; 66506</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19350; 37838</t>
+          <t>19584; 38971</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53987; 94741</t>
+          <t>53908; 95609</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1235; 8243</t>
+          <t>1207; 8942</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>676; 6463</t>
+          <t>676; 5848</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2498; 11079</t>
+          <t>2424; 10882</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78727; 127369</t>
+          <t>79632; 129356</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>118207; 167507</t>
+          <t>120665; 167421</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>215396; 283559</t>
+          <t>219208; 289454</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraNOcobra-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,62</t>
+          <t>8,61; 12,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,45; 17,23</t>
+          <t>13,3; 16,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 15,21</t>
+          <t>11,89; 14,57</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,91</t>
+          <t>1,42; 2,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,74</t>
+          <t>1,1; 1,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,11</t>
+          <t>1,38; 2,09</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,38</t>
+          <t>0,17; 1,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,09; 1,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,83</t>
+          <t>0,21; 0,84</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,75</t>
+          <t>2,59; 3,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,58</t>
+          <t>3,75; 4,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,07</t>
+          <t>3,32; 4,09</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57719</t>
+          <t>60662</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>115795</t>
+          <t>123036</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173514</t>
+          <t>183698</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>46574; 70118</t>
+          <t>49793; 74130</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>101652; 130175</t>
+          <t>109327; 139366</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>156426; 193177</t>
+          <t>166514; 204055</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>43934</t>
+          <t>42531</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28218</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72152</t>
+          <t>74507</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28289; 66506</t>
+          <t>31745; 57661</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19584; 38971</t>
+          <t>23827; 41642</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53908; 95609</t>
+          <t>60654; 91991</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>6513</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1207; 8942</t>
+          <t>1202; 8225</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>676; 5848</t>
+          <t>685; 7422</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2424; 10882</t>
+          <t>3066; 12129</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>106749</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>146251</t>
+          <t>157969</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251375</t>
+          <t>264718</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79632; 129356</t>
+          <t>91221; 130767</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>120665; 167421</t>
+          <t>139917; 177589</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>219208; 289454</t>
+          <t>240726; 296122</t>
         </is>
       </c>
     </row>
